--- a/기본서/26컴활2급/이론/함수.xlsx
+++ b/기본서/26컴활2급/이론/함수.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\public\mbc\agi_excel_2026_07\public\기본서\26컴활2급\이론\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2EADFF-78FC-4E59-826B-301AA657AE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95EAF23-C8A0-44F6-A466-95A7527EE154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{FAEC01E4-8891-488A-969B-48B02C20ED40}"/>
   </bookViews>
@@ -973,7 +973,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="2:11" ht="66" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" ht="33" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>26</v>
       </c>
@@ -1567,7 +1567,7 @@
     <row r="20" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E20">
         <f ca="1">RAND()</f>
-        <v>0.95390677660566769</v>
+        <v>5.4509404516299265E-2</v>
       </c>
       <c r="F20" t="s">
         <v>47</v>
@@ -1579,7 +1579,7 @@
     <row r="21" spans="5:7" x14ac:dyDescent="0.3">
       <c r="E21">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
         <v>49</v>
